--- a/cleaning_forms/022_home_cleaning_service_referral_form--cleaning_forms.xlsx
+++ b/cleaning_forms/022_home_cleaning_service_referral_form--cleaning_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>utm_term_id</t>
+          <t>utm_term_id_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>utm_term_id</t>
+          <t>Utm Term Id 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>utm_medium</t>
+          <t>utm_medium_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>utm_medium</t>
+          <t>Utm Medium 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>utm_source</t>
+          <t>utm_source_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>utm_source</t>
+          <t>Utm Source 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1148,8 +1148,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'option 1', 'value': '1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1194,80 +1194,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'option 2', 'value': '2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>utm_medium_choices</t>
+          <t>utm_medium_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'utm_medium_1',_'value':_'1'}</t>
+          <t>utm_medium_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'utm_medium 1', 'value': '1'}</t>
+          <t>utm medium 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>utm_medium_choices</t>
+          <t>utm_medium_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'utm_medium_2',_'value':_'2'}</t>
+          <t>utm_medium_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'utm_medium 2', 'value': '2'}</t>
+          <t>utm medium 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>utm_source_choices</t>
+          <t>utm_source_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'utm_source_1',_'value':_'1'}</t>
+          <t>utm_source_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'utm_source 1', 'value': '1'}</t>
+          <t>utm source 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>utm_source_choices</t>
+          <t>utm_source_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'utm_source_2',_'value':_'2'}</t>
+          <t>utm_source_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'utm_source 2', 'value': '2'}</t>
+          <t>utm source 2</t>
         </is>
       </c>
     </row>
